--- a/DataTables/Datas/#VSPickup.xlsx
+++ b/DataTables/Datas/#VSPickup.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,6 +442,11 @@
           <t>value</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>entityId</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -469,6 +474,11 @@
           <t>int</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -494,6 +504,11 @@
       <c r="E3" t="inlineStr">
         <is>
           <t>效果值(经验/治疗量等)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>表现实体id(#Entity,0=暂未实现)</t>
         </is>
       </c>
     </row>
@@ -514,6 +529,9 @@
       <c r="E4" t="n">
         <v>1</v>
       </c>
+      <c r="F4" t="n">
+        <v>300001</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="n">
@@ -532,6 +550,9 @@
       <c r="E5" t="n">
         <v>30</v>
       </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="n">
@@ -550,6 +571,9 @@
       <c r="E6" t="n">
         <v>0</v>
       </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="n">
@@ -566,7 +590,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="F7" t="n">
+        <v>300002</v>
       </c>
     </row>
   </sheetData>
